--- a/results/Int Task Remove ACC 0.7/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC 0.7/Rando_9_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.652329517059652</v>
+        <v>0.6384307846076962</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6526429966834765</v>
+        <v>0.6299634273772204</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6535834355549498</v>
+        <v>0.6347712507382672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6538969151787742</v>
+        <v>0.6420176275498615</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6291615555858434</v>
+        <v>0.6404502294307391</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6212189359865522</v>
+        <v>0.628953704965699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6316693925764391</v>
+        <v>0.6265844350551997</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6295443187497161</v>
+        <v>0.633203852619145</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6264788060515196</v>
+        <v>0.6295806642133479</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6286038798782427</v>
+        <v>0.620347780655127</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6126130116759803</v>
+        <v>0.645152423788106</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6135534505474536</v>
+        <v>0.6578335832083958</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.608187951478806</v>
+        <v>0.6578335832083958</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6118111398846031</v>
+        <v>0.6578335832083958</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.609616782517832</v>
+        <v>0.6545238744264231</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6093033028940076</v>
+        <v>0.6633376493571397</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6095474989777838</v>
+        <v>0.66790127663441</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6074224251510608</v>
+        <v>0.6519433465085639</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6074224251510608</v>
+        <v>0.6492605969742402</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6331675071555132</v>
+        <v>0.6456737540320749</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6053302894007542</v>
+        <v>0.6450467947844261</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6053302894007542</v>
+        <v>0.6290922720457953</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6365794375539503</v>
+        <v>0.6390213983917132</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6275214665394575</v>
+        <v>0.6390213983917132</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6368929171777747</v>
+        <v>0.6380809595202399</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6365794375539503</v>
+        <v>0.6344577711144428</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6383910317568489</v>
+        <v>0.6468254509109082</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6317716141929035</v>
+        <v>0.6484621325700786</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6154672663668166</v>
+        <v>0.6484621325700786</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6314581345690791</v>
+        <v>0.6394041615555859</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6169653809458907</v>
+        <v>0.6509006860206261</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6085707146426786</v>
+        <v>0.6583219753759484</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6079437553950298</v>
+        <v>0.6546987869701513</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5461053564127027</v>
+        <v>0.6546987869701513</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5450956340011812</v>
+        <v>0.6461984916632593</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5496592612784517</v>
+        <v>0.6480793694062059</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5496592612784517</v>
+        <v>0.680862977602108</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5472899913679524</v>
+        <v>0.6631990822770433</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5591363409204488</v>
+        <v>0.671560810503839</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5591363409204488</v>
+        <v>0.667310662850393</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5591363409204488</v>
+        <v>0.667310662850393</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5353414201989914</v>
+        <v>0.6398925537231385</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5242969424378719</v>
+        <v>0.6350847303620917</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5211621461996274</v>
+        <v>0.5907353141611013</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5168790604697651</v>
+        <v>0.5907353141611013</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5511971287083731</v>
+        <v>0.6145302348825588</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5530087229112717</v>
+        <v>0.6573815365044751</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5972559174957977</v>
+        <v>0.6247728408523011</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4560901367498069</v>
+        <v>0.6217073281541048</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4600960883194766</v>
+        <v>0.7364647221843623</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4638249057289537</v>
+        <v>0.7505747126436781</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4428513016219163</v>
+        <v>0.748380355276907</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4105629003679978</v>
+        <v>0.7559402117123257</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4236597610285766</v>
+        <v>0.7951683249284449</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4267945572668211</v>
+        <v>0.7948548453046205</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4148459860978602</v>
+        <v>0.7926604879378493</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.412545999727409</v>
+        <v>0.7926604879378493</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4119190404797601</v>
+        <v>0.7140656944255146</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.418119349416201</v>
+        <v>0.7033710417518513</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.3977397664803962</v>
+        <v>0.7051826359547499</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.3977397664803962</v>
+        <v>0.6705215574031167</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.392618463495525</v>
+        <v>0.6789855072463769</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.394637908318568</v>
+        <v>0.6557482622325201</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4057153241561038</v>
+        <v>0.6997478533460543</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.396762982145291</v>
+        <v>0.6772341102176185</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.396762982145291</v>
+        <v>0.6762607332697288</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4257518967788833</v>
+        <v>0.517515106083322</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4257518967788833</v>
+        <v>0.517515106083322</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4224092499204943</v>
+        <v>0.517515106083322</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4155456362727727</v>
+        <v>0.5172016264594975</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4343714506383172</v>
+        <v>0.4921925400935896</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4417893326064241</v>
+        <v>0.4911464722184362</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4393507791558766</v>
+        <v>0.4712518740629685</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4278213166144201</v>
+        <v>0.4593725864340557</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4394234700831402</v>
+        <v>0.4774885284630412</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4736029712416519</v>
+        <v>0.5006564899368497</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.477226159647449</v>
+        <v>0.5091238471673254</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.473286084230612</v>
+        <v>0.5011482894916178</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4595418199990914</v>
+        <v>0.5013924855753941</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4645574939802826</v>
+        <v>0.5007655263277452</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4597496706192359</v>
+        <v>0.4980134932533733</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4168756530825496</v>
+        <v>0.5013924855753941</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4458872836309118</v>
+        <v>0.5028906001544682</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4364102039889146</v>
+        <v>0.5018808777429468</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4820169460724183</v>
+        <v>0.5018808777429468</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6045170596519922</v>
+        <v>0.5006269592476489</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5612602789514334</v>
+        <v>0.5003134796238244</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.511739584753078</v>
+        <v>0.5018808777429468</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.511739584753078</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
